--- a/data/estructura_comercial.xlsx
+++ b/data/estructura_comercial.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\a subir mas analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93398B2E-82D0-47CA-8453-B2433F8F21F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B10A84-F8FE-4EC7-B73E-E3192517AB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Estructura!$A$1:$D$33</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -97,9 +100,6 @@
     <t>GONZALEZ CANDELARIA</t>
   </si>
   <si>
-    <t>MARIANO TRIULICI</t>
-  </si>
-  <si>
     <t>RESTIVO VALERIA</t>
   </si>
   <si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>SANCHEZ JULIAN</t>
+  </si>
+  <si>
+    <t>SEBASTIAN SANCHEZ</t>
   </si>
 </sst>
 </file>
@@ -767,13 +770,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>500</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>42</v>
@@ -781,13 +784,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>500</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <v>43</v>
@@ -795,13 +798,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B23">
         <v>500</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23">
         <v>44</v>
@@ -809,13 +812,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>500</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>46</v>
@@ -823,13 +826,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>500</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>47</v>
@@ -837,13 +840,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B26">
         <v>500</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>48</v>
@@ -851,13 +854,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>500</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>54</v>
@@ -865,13 +868,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>500</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>58</v>
@@ -885,7 +888,7 @@
         <v>600</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>61</v>
@@ -899,7 +902,7 @@
         <v>600</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>62</v>
@@ -913,7 +916,7 @@
         <v>600</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>63</v>
@@ -927,7 +930,7 @@
         <v>600</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32">
         <v>64</v>
@@ -941,13 +944,14 @@
         <v>600</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33">
         <v>65</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D33" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>